--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB90CAC7-0EF7-4EAA-8204-8EEB8729785D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDF52C3-0ADE-4ED1-8550-C18CF73ABA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="2190" yWindow="2250" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -112,12 +112,6 @@
     <t>Autre</t>
   </si>
   <si>
-    <t>Nom Prénom</t>
-  </si>
-  <si>
-    <t>18.03.2024  au 27.05.2024</t>
-  </si>
-  <si>
     <t>P_App - 335 - Passion Lecture</t>
   </si>
   <si>
@@ -140,6 +134,15 @@
   </si>
   <si>
     <t>Update des maquettes pour adérer auc demandes dans le CdC</t>
+  </si>
+  <si>
+    <t>Mise en place du projet Vue.js et apprentissage sur le site vue.js</t>
+  </si>
+  <si>
+    <t>Moser Charles-Henri</t>
+  </si>
+  <si>
+    <t>08.04.2025  au 26.05.2025</t>
   </si>
 </sst>
 </file>
@@ -2031,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D2" s="57"/>
       <c r="E2" s="57"/>
@@ -2039,7 +2042,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
@@ -2056,7 +2059,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="23.25" hidden="1" x14ac:dyDescent="0.35">
@@ -2090,19 +2093,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -2121,7 +2124,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" s="54"/>
     </row>
@@ -2141,7 +2144,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" s="55"/>
       <c r="M8" t="s">
@@ -2170,7 +2173,7 @@
         <v>7</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G9" s="56"/>
       <c r="M9" t="s">
@@ -2199,7 +2202,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G10" s="55"/>
       <c r="M10" t="s">
@@ -2227,7 +2230,9 @@
       <c r="E11" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="36"/>
+      <c r="F11" s="36" t="s">
+        <v>31</v>
+      </c>
       <c r="G11" s="56"/>
       <c r="M11" t="s">
         <v>6</v>
@@ -8788,6 +8793,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9010,17 +9026,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9030,6 +9035,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9046,15 +9062,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDF52C3-0ADE-4ED1-8550-C18CF73ABA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6E91DE-A1C5-4BC8-ACB5-E1E52511062F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="2190" yWindow="2250" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="3090" yWindow="1230" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -143,6 +143,15 @@
   </si>
   <si>
     <t>08.04.2025  au 26.05.2025</t>
+  </si>
+  <si>
+    <t>Discussion avec Antoine sur le travail que l'on fait aujourd'hui.</t>
+  </si>
+  <si>
+    <t>Retour avec Antoine sur la Maquette.</t>
+  </si>
+  <si>
+    <t>Base pour le Footeur: Fonctionnel et s'affiche dans la page d'acceuil</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1082,7 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3888888888888888E-2</c:v>
+                  <c:v>6.5972222222222224E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1082,13 +1091,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.8611111111111112E-2</c:v>
+                  <c:v>6.25E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.1666666666666664E-2</c:v>
+                  <c:v>4.8611111111111112E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -2051,7 +2060,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 3 heurs 0 minutes</v>
+        <v>0 jours 4 heurs 45 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2066,15 +2075,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="22">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2245,15 +2254,23 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+      <c r="A12" s="8">
         <f>IF(ISBLANK(B12),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B12))</f>
-        <v/>
-      </c>
-      <c r="B12" s="46"/>
+        <v>16</v>
+      </c>
+      <c r="B12" s="46">
+        <v>45767</v>
+      </c>
       <c r="C12" s="47"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="36"/>
+      <c r="D12" s="48">
+        <v>20</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="36" t="s">
+        <v>34</v>
+      </c>
       <c r="G12" s="55"/>
       <c r="M12" t="s">
         <v>7</v>
@@ -2266,15 +2283,23 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="str">
+      <c r="A13" s="16">
         <f>IF(ISBLANK(B13),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B13))</f>
-        <v/>
-      </c>
-      <c r="B13" s="50"/>
+        <v>16</v>
+      </c>
+      <c r="B13" s="50">
+        <v>45767</v>
+      </c>
       <c r="C13" s="51"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="36"/>
+      <c r="D13" s="52">
+        <v>10</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>35</v>
+      </c>
       <c r="G13" s="56"/>
       <c r="M13" t="s">
         <v>8</v>
@@ -2287,15 +2312,25 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+      <c r="A14" s="8">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
-        <v/>
-      </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="36"/>
+        <v>16</v>
+      </c>
+      <c r="B14" s="46">
+        <v>45767</v>
+      </c>
+      <c r="C14" s="47">
+        <v>1</v>
+      </c>
+      <c r="D14" s="48">
+        <v>15</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>36</v>
+      </c>
       <c r="G14" s="55"/>
       <c r="M14" t="s">
         <v>21</v>
@@ -8641,11 +8676,11 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8653,7 +8688,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>1.3888888888888888E-2</v>
+        <v>6.5972222222222224E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -8699,7 +8734,7 @@
       </c>
       <c r="B8">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C8,'Journal de travail'!$D$7:$D$532)</f>
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C8" s="28" t="str">
         <f>'Journal de travail'!M12</f>
@@ -8707,7 +8742,7 @@
       </c>
       <c r="D8" s="33">
         <f t="shared" si="0"/>
-        <v>4.8611111111111112E-2</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -8735,7 +8770,7 @@
       </c>
       <c r="B10">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C10,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C10" s="37" t="str">
         <f>'Journal de travail'!M14</f>
@@ -8743,7 +8778,7 @@
       </c>
       <c r="D10" s="33">
         <f t="shared" si="0"/>
-        <v>4.1666666666666664E-2</v>
+        <v>4.8611111111111112E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -8770,7 +8805,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.125</v>
+        <v>0.19791666666666666</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -8793,17 +8828,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9026,6 +9050,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9035,17 +9070,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9062,4 +9086,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6E91DE-A1C5-4BC8-ACB5-E1E52511062F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B2E256-7148-410A-9D38-DC5ECDE4A5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="1230" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -152,6 +152,12 @@
   </si>
   <si>
     <t>Base pour le Footeur: Fonctionnel et s'affiche dans la page d'acceuil</t>
+  </si>
+  <si>
+    <t>Footer presque fini.</t>
+  </si>
+  <si>
+    <t>Page d'acceuil coupée en 2 donc doit refaire code pour cela.</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1088,7 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.5972222222222224E-2</c:v>
+                  <c:v>9.7222222222222224E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2060,7 +2066,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 4 heurs 45 minutes</v>
+        <v>0 jours 5 heurs 30 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2079,11 +2085,11 @@
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2256,10 +2262,10 @@
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <f>IF(ISBLANK(B12),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B12))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="46">
-        <v>45767</v>
+        <v>45776</v>
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="48">
@@ -2285,10 +2291,10 @@
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <f>IF(ISBLANK(B13),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B13))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" s="50">
-        <v>45767</v>
+        <v>45776</v>
       </c>
       <c r="C13" s="51"/>
       <c r="D13" s="52">
@@ -2314,10 +2320,10 @@
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B14" s="46">
-        <v>45767</v>
+        <v>45776</v>
       </c>
       <c r="C14" s="47">
         <v>1</v>
@@ -2343,16 +2349,26 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="str">
+      <c r="A15" s="16">
         <f>IF(ISBLANK(B15),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B15))</f>
-        <v/>
-      </c>
-      <c r="B15" s="50"/>
+        <v>18</v>
+      </c>
+      <c r="B15" s="50">
+        <v>45777</v>
+      </c>
       <c r="C15" s="51"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="56"/>
+      <c r="D15" s="52">
+        <v>45</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="56" t="s">
+        <v>38</v>
+      </c>
       <c r="M15" t="s">
         <v>22</v>
       </c>
@@ -2364,11 +2380,13 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+      <c r="A16" s="8">
         <f>IF(ISBLANK(B16),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B16))</f>
-        <v/>
-      </c>
-      <c r="B16" s="46"/>
+        <v>18</v>
+      </c>
+      <c r="B16" s="46">
+        <v>45777</v>
+      </c>
       <c r="C16" s="47"/>
       <c r="D16" s="48"/>
       <c r="E16" s="49"/>
@@ -8680,7 +8698,7 @@
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8688,7 +8706,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>6.5972222222222224E-2</v>
+        <v>9.7222222222222224E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -8805,7 +8823,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.19791666666666666</v>
+        <v>0.22916666666666666</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -8828,6 +8846,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9050,17 +9079,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9070,6 +9088,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9086,15 +9115,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B2E256-7148-410A-9D38-DC5ECDE4A5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4633AAE0-11BF-45AA-95C6-E9CE246EECA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="1230" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -158,6 +158,12 @@
   </si>
   <si>
     <t>Page d'acceuil coupée en 2 donc doit refaire code pour cela.</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>DropDown Menu avec Antoine Piguet</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1094,7 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.7222222222222224E-2</c:v>
+                  <c:v>0.19097222222222221</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2066,7 +2072,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 5 heurs 30 minutes</v>
+        <v>0 jours 7 heurs 45 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2081,15 +2087,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="22">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>330</v>
+        <v>465</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2388,24 +2394,40 @@
         <v>45777</v>
       </c>
       <c r="C16" s="47"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="36"/>
+      <c r="D16" s="48">
+        <v>45</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="G16" s="55"/>
       <c r="O16">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="str">
+      <c r="A17" s="16">
         <f>IF(ISBLANK(B17),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="36"/>
+        <v>18</v>
+      </c>
+      <c r="B17" s="50">
+        <v>45777</v>
+      </c>
+      <c r="C17" s="51">
+        <v>1</v>
+      </c>
+      <c r="D17" s="52">
+        <v>30</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="36" t="s">
+        <v>40</v>
+      </c>
       <c r="G17" s="56"/>
       <c r="O17">
         <v>45</v>
@@ -8694,11 +8716,11 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8706,7 +8728,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>9.7222222222222224E-2</v>
+        <v>0.19097222222222221</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -8823,7 +8845,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.22916666666666666</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -8846,17 +8868,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9079,6 +9090,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9088,17 +9110,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9115,4 +9126,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4633AAE0-11BF-45AA-95C6-E9CE246EECA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A6C8D8-B280-4A35-949F-2168228D1A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="1230" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -164,6 +164,15 @@
   </si>
   <si>
     <t>DropDown Menu avec Antoine Piguet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changements dans le Header et la sidebare </t>
+  </si>
+  <si>
+    <t>Documentations dans ce journal de travail</t>
+  </si>
+  <si>
+    <t>Début de la page profile</t>
   </si>
 </sst>
 </file>
@@ -1094,13 +1103,13 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.19097222222222221</c:v>
+                  <c:v>0.27777777777777779</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.472222222222222E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>6.25E-2</c:v>
@@ -2072,7 +2081,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 7 heurs 45 minutes</v>
+        <v>0 jours 9 heurs 55 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2087,15 +2096,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="22">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>285</v>
+        <v>355</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>465</v>
+        <v>595</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2434,45 +2443,71 @@
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+      <c r="A18" s="8">
         <f>IF(ISBLANK(B18),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="36"/>
+        <v>19</v>
+      </c>
+      <c r="B18" s="46">
+        <v>45783</v>
+      </c>
+      <c r="C18" s="47">
+        <v>1</v>
+      </c>
+      <c r="D18" s="48">
+        <v>25</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>41</v>
+      </c>
       <c r="G18" s="55"/>
       <c r="O18">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="str">
+      <c r="A19" s="16">
         <f>IF(ISBLANK(B19),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="50"/>
+        <v>19</v>
+      </c>
+      <c r="B19" s="50">
+        <v>45783</v>
+      </c>
       <c r="C19" s="51"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="36"/>
+      <c r="D19" s="52">
+        <v>40</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>43</v>
+      </c>
       <c r="G19" s="56"/>
       <c r="O19">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+      <c r="A20" s="8">
         <f>IF(ISBLANK(B20),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="46"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="46">
+        <v>45783</v>
+      </c>
       <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="36"/>
+      <c r="D20" s="48">
+        <v>5</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>42</v>
+      </c>
       <c r="G20" s="55"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -8716,11 +8751,11 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8728,7 +8763,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>0.19097222222222221</v>
+        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -8756,7 +8791,7 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7" s="27" t="str">
         <f>'Journal de travail'!M11</f>
@@ -8764,7 +8799,7 @@
       </c>
       <c r="D7" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.472222222222222E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -8845,7 +8880,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.32291666666666669</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -8868,6 +8903,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9090,17 +9136,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9110,6 +9145,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9126,15 +9172,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A6C8D8-B280-4A35-949F-2168228D1A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18C40CD-3496-4FA5-B5B4-39DA46DE9E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -173,6 +173,18 @@
   </si>
   <si>
     <t>Début de la page profile</t>
+  </si>
+  <si>
+    <t>Mini Meeting avec l'équipe répartitions des tâches</t>
+  </si>
+  <si>
+    <t>Ajout du composant page Profile.vue</t>
+  </si>
+  <si>
+    <t>Manque les connetions avec la database et les actions CRUD</t>
+  </si>
+  <si>
+    <t>Ajout du service api Axios</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1115,7 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.27777777777777779</c:v>
+                  <c:v>0.33680555555555558</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1112,7 +1124,7 @@
                   <c:v>3.472222222222222E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.25E-2</c:v>
+                  <c:v>6.5972222222222224E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -2081,7 +2093,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 9 heurs 55 minutes</v>
+        <v>0 jours 11 heurs 25 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2100,11 +2112,11 @@
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>355</v>
+        <v>445</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>595</v>
+        <v>685</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2511,39 +2523,65 @@
       <c r="G20" s="55"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="str">
+      <c r="A21" s="16">
         <f>IF(ISBLANK(B21),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="50"/>
+        <v>19</v>
+      </c>
+      <c r="B21" s="50">
+        <v>45784</v>
+      </c>
       <c r="C21" s="51"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="36"/>
+      <c r="D21" s="52">
+        <v>5</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>44</v>
+      </c>
       <c r="G21" s="56"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+      <c r="A22" s="8">
         <f>IF(ISBLANK(B22),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="46"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="46">
+        <v>45784</v>
+      </c>
       <c r="C22" s="47"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="55"/>
+      <c r="D22" s="48">
+        <v>55</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="55" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="str">
+      <c r="A23" s="16">
         <f>IF(ISBLANK(B23),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="50"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="50">
+        <v>45784</v>
+      </c>
       <c r="C23" s="51"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="36"/>
+      <c r="D23" s="52">
+        <v>30</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>47</v>
+      </c>
       <c r="G23" s="56"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -8755,7 +8793,7 @@
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8763,7 +8801,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>0.27777777777777779</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -8809,7 +8847,7 @@
       </c>
       <c r="B8">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C8,'Journal de travail'!$D$7:$D$532)</f>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C8" s="28" t="str">
         <f>'Journal de travail'!M12</f>
@@ -8817,7 +8855,7 @@
       </c>
       <c r="D8" s="33">
         <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <v>6.5972222222222224E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -8880,7 +8918,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.41319444444444442</v>
+        <v>0.47569444444444442</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -8903,17 +8941,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9136,6 +9163,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9145,17 +9183,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9172,4 +9199,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18C40CD-3496-4FA5-B5B4-39DA46DE9E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAF5F37-2112-4602-B1D4-2B25E769B733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -185,6 +185,15 @@
   </si>
   <si>
     <t>Ajout du service api Axios</t>
+  </si>
+  <si>
+    <t>Problème lord de modification d'images</t>
+  </si>
+  <si>
+    <t>Supprime anciant code inutile dans lequel j'ai confondu mes modifications</t>
+  </si>
+  <si>
+    <t>Ajout page DetailsBook.vue</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1124,7 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.33680555555555558</c:v>
+                  <c:v>0.39583333333333331</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2093,7 +2102,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 11 heurs 25 minutes</v>
+        <v>0 jours 12 heurs 49 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2112,11 +2121,11 @@
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>445</v>
+        <v>530</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>685</v>
+        <v>770</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2585,27 +2594,45 @@
       <c r="G23" s="56"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+      <c r="A24" s="8">
         <f>IF(ISBLANK(B24),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="46"/>
+        <v>19</v>
+      </c>
+      <c r="B24" s="46">
+        <v>45784</v>
+      </c>
       <c r="C24" s="47"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="55"/>
+      <c r="D24" s="48">
+        <v>30</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="55" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="str">
+      <c r="A25" s="16">
         <f>IF(ISBLANK(B25),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B25))</f>
-        <v/>
-      </c>
-      <c r="B25" s="50"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="50">
+        <v>45784</v>
+      </c>
       <c r="C25" s="51"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="36"/>
+      <c r="D25" s="52">
+        <v>55</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>50</v>
+      </c>
       <c r="G25" s="56"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -8793,7 +8820,7 @@
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>305</v>
+        <v>390</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8801,7 +8828,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>0.33680555555555558</v>
+        <v>0.39583333333333331</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -8918,7 +8945,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.47569444444444442</v>
+        <v>0.53472222222222221</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -8941,6 +8968,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9163,17 +9201,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9183,6 +9210,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9199,15 +9237,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAF5F37-2112-4602-B1D4-2B25E769B733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1970BC24-C689-4768-91C5-50BFCF25255F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -193,7 +193,16 @@
     <t>Supprime anciant code inutile dans lequel j'ai confondu mes modifications</t>
   </si>
   <si>
-    <t>Ajout page DetailsBook.vue</t>
+    <t>Ajout page DetailsBook.vue Template</t>
+  </si>
+  <si>
+    <t>Details view de chaque livre fonctionnel avec communication DB</t>
+  </si>
+  <si>
+    <t>Ajout de la page Register Template</t>
+  </si>
+  <si>
+    <t>Peer-Working Avec Antoine Piguet sur une erreur chez lui</t>
   </si>
 </sst>
 </file>
@@ -1124,13 +1133,13 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39583333333333331</c:v>
+                  <c:v>0.54513888888888884</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.472222222222222E-3</c:v>
+                  <c:v>1.0416666666666666E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>6.5972222222222224E-2</c:v>
@@ -2102,7 +2111,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 12 heurs 49 minutes</v>
+        <v>0 jours 16 heurs 34 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2117,15 +2126,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="22">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>530</v>
+        <v>635</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>770</v>
+        <v>995</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2636,51 +2645,85 @@
       <c r="G25" s="56"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="str">
+      <c r="A26" s="8">
         <f>IF(ISBLANK(B26),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B26))</f>
-        <v/>
-      </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="36"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="46">
+        <v>45790</v>
+      </c>
+      <c r="C26" s="47">
+        <v>2</v>
+      </c>
+      <c r="D26" s="48">
+        <v>15</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>51</v>
+      </c>
       <c r="G26" s="55"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="str">
+      <c r="A27" s="16">
         <f>IF(ISBLANK(B27),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B27))</f>
-        <v/>
-      </c>
-      <c r="B27" s="50"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="50">
+        <v>45790</v>
+      </c>
       <c r="C27" s="51"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="36"/>
+      <c r="D27" s="52">
+        <v>40</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>52</v>
+      </c>
       <c r="G27" s="56"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="str">
+      <c r="A28" s="8">
         <f>IF(ISBLANK(B28),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B28))</f>
-        <v/>
-      </c>
-      <c r="B28" s="46"/>
+        <v>20</v>
+      </c>
+      <c r="B28" s="46">
+        <v>45790</v>
+      </c>
       <c r="C28" s="47"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="35"/>
+      <c r="D28" s="48">
+        <v>40</v>
+      </c>
+      <c r="E28" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>53</v>
+      </c>
       <c r="G28" s="55"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="str">
+      <c r="A29" s="16">
         <f>IF(ISBLANK(B29),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B29))</f>
-        <v/>
-      </c>
-      <c r="B29" s="50"/>
+        <v>20</v>
+      </c>
+      <c r="B29" s="50">
+        <v>45790</v>
+      </c>
       <c r="C29" s="51"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="35"/>
+      <c r="D29" s="52">
+        <v>10</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>0</v>
+      </c>
       <c r="G29" s="56"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -8816,11 +8859,11 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>390</v>
+        <v>485</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8828,7 +8871,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>0.39583333333333331</v>
+        <v>0.54513888888888884</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -8856,7 +8899,7 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C7" s="27" t="str">
         <f>'Journal de travail'!M11</f>
@@ -8864,7 +8907,7 @@
       </c>
       <c r="D7" s="33">
         <f t="shared" si="0"/>
-        <v>3.472222222222222E-3</v>
+        <v>1.0416666666666666E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -8945,7 +8988,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.53472222222222221</v>
+        <v>0.69097222222222221</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -8968,17 +9011,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9201,6 +9233,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9210,17 +9253,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9237,4 +9269,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1970BC24-C689-4768-91C5-50BFCF25255F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34B4FC5-0F0B-4C2A-9B99-C2D4A85DD9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="61">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -203,6 +203,27 @@
   </si>
   <si>
     <t>Peer-Working Avec Antoine Piguet sur une erreur chez lui</t>
+  </si>
+  <si>
+    <t>Update de la page Details.vue pour que les étoiles s'affichent</t>
+  </si>
+  <si>
+    <t>Update du service API afin d'utiliser fetch à la place de Axios</t>
+  </si>
+  <si>
+    <t>Création de la page Mybooks, avec token d'authentification</t>
+  </si>
+  <si>
+    <t>Retravaillage de la page vue, pour que le header ne s'affiche pas sur le titre.</t>
+  </si>
+  <si>
+    <t>Creation de la page EditBooks + ajout de bouton pour modifier les données du livre que l'utilisateur à créer</t>
+  </si>
+  <si>
+    <t>Durant la journée, peer programming avec Antoine Piguet</t>
+  </si>
+  <si>
+    <t>update BooksView problème de routage.</t>
   </si>
 </sst>
 </file>
@@ -1133,13 +1154,13 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.54513888888888884</c:v>
+                  <c:v>0.69444444444444442</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0416666666666666E-2</c:v>
+                  <c:v>1.7361111111111112E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>6.5972222222222224E-2</c:v>
@@ -2111,7 +2132,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 16 heurs 34 minutes</v>
+        <v>0 jours 20 heurs 19 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2130,11 +2151,11 @@
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>635</v>
+        <v>860</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>995</v>
+        <v>1220</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2727,107 +2748,173 @@
       <c r="G29" s="56"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="str">
+      <c r="A30" s="8">
         <f>IF(ISBLANK(B30),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B30))</f>
-        <v/>
-      </c>
-      <c r="B30" s="46"/>
+        <v>21</v>
+      </c>
+      <c r="B30" s="46">
+        <v>45797</v>
+      </c>
       <c r="C30" s="47"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="36"/>
+      <c r="D30" s="48">
+        <v>50</v>
+      </c>
+      <c r="E30" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>54</v>
+      </c>
       <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="str">
+      <c r="A31" s="16">
         <f>IF(ISBLANK(B31),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B31))</f>
-        <v/>
-      </c>
-      <c r="B31" s="50"/>
+        <v>21</v>
+      </c>
+      <c r="B31" s="50">
+        <v>45797</v>
+      </c>
       <c r="C31" s="51"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="35"/>
+      <c r="D31" s="52">
+        <v>20</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>55</v>
+      </c>
       <c r="G31" s="56"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="str">
+      <c r="A32" s="8">
         <f>IF(ISBLANK(B32),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B32))</f>
-        <v/>
-      </c>
-      <c r="B32" s="46"/>
+        <v>21</v>
+      </c>
+      <c r="B32" s="46">
+        <v>45797</v>
+      </c>
       <c r="C32" s="47"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="36"/>
+      <c r="D32" s="48">
+        <v>50</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>56</v>
+      </c>
       <c r="G32" s="55"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="str">
+      <c r="A33" s="16">
         <f>IF(ISBLANK(B33),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B33))</f>
-        <v/>
-      </c>
-      <c r="B33" s="50"/>
+        <v>21</v>
+      </c>
+      <c r="B33" s="50">
+        <v>45797</v>
+      </c>
       <c r="C33" s="51"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="35"/>
+      <c r="D33" s="52">
+        <v>5</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="G33" s="56"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="str">
+      <c r="A34" s="8">
         <f>IF(ISBLANK(B34),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B34))</f>
-        <v/>
-      </c>
-      <c r="B34" s="46"/>
+        <v>21</v>
+      </c>
+      <c r="B34" s="46">
+        <v>45797</v>
+      </c>
       <c r="C34" s="47"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="35"/>
+      <c r="D34" s="48">
+        <v>40</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>58</v>
+      </c>
       <c r="G34" s="55"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="str">
+      <c r="A35" s="16">
         <f>IF(ISBLANK(B35),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B35))</f>
-        <v/>
-      </c>
-      <c r="B35" s="50"/>
+        <v>21</v>
+      </c>
+      <c r="B35" s="50">
+        <v>45797</v>
+      </c>
       <c r="C35" s="51"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="36"/>
+      <c r="D35" s="52">
+        <v>30</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="36" t="s">
+        <v>59</v>
+      </c>
       <c r="G35" s="56"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="str">
+      <c r="A36" s="8">
         <f>IF(ISBLANK(B36),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B36))</f>
-        <v/>
-      </c>
-      <c r="B36" s="46"/>
+        <v>21</v>
+      </c>
+      <c r="B36" s="46">
+        <v>45797</v>
+      </c>
       <c r="C36" s="47"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="35"/>
+      <c r="D36" s="48">
+        <v>20</v>
+      </c>
+      <c r="E36" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="35" t="s">
+        <v>60</v>
+      </c>
       <c r="G36" s="55"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="str">
+      <c r="A37" s="16">
         <f>IF(ISBLANK(B37),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B37))</f>
-        <v/>
-      </c>
-      <c r="B37" s="50"/>
+        <v>21</v>
+      </c>
+      <c r="B37" s="50">
+        <v>45797</v>
+      </c>
       <c r="C37" s="51"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="35"/>
+      <c r="D37" s="52">
+        <v>10</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>0</v>
+      </c>
       <c r="G37" s="56"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="str">
+      <c r="A38" s="8">
         <f>IF(ISBLANK(B38),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B38))</f>
-        <v/>
-      </c>
-      <c r="B38" s="46"/>
+        <v>21</v>
+      </c>
+      <c r="B38" s="46">
+        <v>45798</v>
+      </c>
       <c r="C38" s="47"/>
       <c r="D38" s="48"/>
       <c r="E38" s="49"/>
@@ -2835,11 +2922,13 @@
       <c r="G38" s="55"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="str">
+      <c r="A39" s="16">
         <f>IF(ISBLANK(B39),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B39))</f>
-        <v/>
-      </c>
-      <c r="B39" s="50"/>
+        <v>21</v>
+      </c>
+      <c r="B39" s="50">
+        <v>45798</v>
+      </c>
       <c r="C39" s="51"/>
       <c r="D39" s="52"/>
       <c r="E39" s="53"/>
@@ -2847,11 +2936,13 @@
       <c r="G39" s="56"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="str">
+      <c r="A40" s="8">
         <f>IF(ISBLANK(B40),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B40))</f>
-        <v/>
-      </c>
-      <c r="B40" s="46"/>
+        <v>21</v>
+      </c>
+      <c r="B40" s="46">
+        <v>45798</v>
+      </c>
       <c r="C40" s="47"/>
       <c r="D40" s="48"/>
       <c r="E40" s="49"/>
@@ -8863,7 +8954,7 @@
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>485</v>
+        <v>700</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8871,7 +8962,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>0.54513888888888884</v>
+        <v>0.69444444444444442</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -8899,7 +8990,7 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C7" s="27" t="str">
         <f>'Journal de travail'!M11</f>
@@ -8907,7 +8998,7 @@
       </c>
       <c r="D7" s="33">
         <f t="shared" si="0"/>
-        <v>1.0416666666666666E-2</v>
+        <v>1.7361111111111112E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -8988,7 +9079,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.69097222222222221</v>
+        <v>0.84722222222222232</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -9011,6 +9102,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9233,17 +9335,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9253,6 +9344,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9269,15 +9371,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
+++ b/documentation/JDT-personal/Journal-de-Travail_MoserCharles-Henri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc01zcg\Documents\GitHub\Passion_lecture_FRONTEND\documentation\JDT-personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34B4FC5-0F0B-4C2A-9B99-C2D4A85DD9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ECA6F8-E8E4-47FA-AF3E-A90B297F7FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Mvap2W10CJFFJsnvkGXSiMLvpngxTMJbJsIKFe7Hzjn0XDcmjGuvBC2FjUCZ/hpRpUhUrG1T4kBlDAIo3yqmSQ==" workbookSaltValue="KXjgXOcsUZI/j7UgPKltzw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -224,6 +224,18 @@
   </si>
   <si>
     <t>update BooksView problème de routage.</t>
+  </si>
+  <si>
+    <t>Mise à jour de de la vue my books pour voir les livres de l'utilisateur connecté.</t>
+  </si>
+  <si>
+    <t>userId / token pas encore différentiés</t>
+  </si>
+  <si>
+    <t>Restructuration des fichiers afin de bien différentiers les components des vues.</t>
+  </si>
+  <si>
+    <t>Mini modif, renommage des files pour une meilleure coherce.</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1166,7 @@
                   <c:v>2.0833333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69444444444444442</c:v>
+                  <c:v>0.75694444444444442</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2132,7 +2144,7 @@
       </c>
       <c r="C3" s="22" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 20 heurs 19 minutes</v>
+        <v>0 jours 21 heurs 49 minutes</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="3"/>
@@ -2151,11 +2163,11 @@
       </c>
       <c r="D4" s="22">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>860</v>
+        <v>950</v>
       </c>
       <c r="E4" s="40">
         <f>SUM(C4:D4)</f>
-        <v>1220</v>
+        <v>1310</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2916,10 +2928,18 @@
         <v>45798</v>
       </c>
       <c r="C38" s="47"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="55"/>
+      <c r="D38" s="48">
+        <v>30</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="55" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
@@ -2930,9 +2950,15 @@
         <v>45798</v>
       </c>
       <c r="C39" s="51"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="35"/>
+      <c r="D39" s="52">
+        <v>40</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>63</v>
+      </c>
       <c r="G39" s="56"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,9 +2970,15 @@
         <v>45798</v>
       </c>
       <c r="C40" s="47"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="35"/>
+      <c r="D40" s="48">
+        <v>20</v>
+      </c>
+      <c r="E40" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>64</v>
+      </c>
       <c r="G40" s="55"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -8954,7 +8986,7 @@
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>700</v>
+        <v>790</v>
       </c>
       <c r="C5" s="41" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8962,7 +8994,7 @@
       </c>
       <c r="D5" s="33">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>0.69444444444444442</v>
+        <v>0.75694444444444442</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -9079,7 +9111,7 @@
       </c>
       <c r="D12" s="34">
         <f>SUM(D4:D11)</f>
-        <v>0.84722222222222232</v>
+        <v>0.90972222222222232</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -9102,17 +9134,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="313dbdbec26224d1c2bb7e3c488b2a4e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4739345e3d2c6be79c5ae1a54d02a4a7" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -9335,6 +9356,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
@@ -9344,17 +9376,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FB702A-DCBD-43A8-A34C-6000FD8861AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9371,4 +9392,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>